--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/html league/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13529FC0-5827-4921-93A7-6460AA385E1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="453">
   <si>
     <t>Stage 1</t>
   </si>
@@ -1389,6 +1389,15 @@
   </si>
   <si>
     <t>Pau Miquel</t>
+  </si>
+  <si>
+    <t>Tobias Foss</t>
+  </si>
+  <si>
+    <t>Tim Wellens</t>
+  </si>
+  <si>
+    <t>Sander De Pestel</t>
   </si>
 </sst>
 </file>
@@ -1767,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -6531,6 +6540,88 @@
       </c>
       <c r="M116" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B117" t="s">
+        <v>441</v>
+      </c>
+      <c r="C117" t="s">
+        <v>51</v>
+      </c>
+      <c r="D117" t="s">
+        <v>204</v>
+      </c>
+      <c r="E117" t="s">
+        <v>447</v>
+      </c>
+      <c r="F117" t="s">
+        <v>450</v>
+      </c>
+      <c r="G117" t="s">
+        <v>75</v>
+      </c>
+      <c r="H117" t="s">
+        <v>451</v>
+      </c>
+      <c r="I117" t="s">
+        <v>80</v>
+      </c>
+      <c r="J117" t="s">
+        <v>452</v>
+      </c>
+      <c r="K117" t="s">
+        <v>27</v>
+      </c>
+      <c r="L117" t="s">
+        <v>79</v>
+      </c>
+      <c r="M117" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B118" t="s">
+        <v>441</v>
+      </c>
+      <c r="C118" t="s">
+        <v>55</v>
+      </c>
+      <c r="D118" t="s">
+        <v>204</v>
+      </c>
+      <c r="E118" t="s">
+        <v>180</v>
+      </c>
+      <c r="F118" t="s">
+        <v>443</v>
+      </c>
+      <c r="G118" t="s">
+        <v>169</v>
+      </c>
+      <c r="H118" t="s">
+        <v>145</v>
+      </c>
+      <c r="I118" t="s">
+        <v>387</v>
+      </c>
+      <c r="J118" t="s">
+        <v>282</v>
+      </c>
+      <c r="K118" t="s">
+        <v>450</v>
+      </c>
+      <c r="L118" t="s">
+        <v>103</v>
+      </c>
+      <c r="M118" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/html league/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13529FC0-5827-4921-93A7-6460AA385E1A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2138BF29-1984-41BD-96D5-9B4F146DFFCC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="449">
   <si>
     <t>Stage 1</t>
   </si>
@@ -518,9 +518,6 @@
     <t>Stage 6</t>
   </si>
   <si>
-    <t>T. H. Johannessen</t>
-  </si>
-  <si>
     <t>David Gaudu</t>
   </si>
   <si>
@@ -596,9 +593,6 @@
     <t>Egan Bernal</t>
   </si>
   <si>
-    <t>Jefferson Cepeda</t>
-  </si>
-  <si>
     <t>Igor Arrieta</t>
   </si>
   <si>
@@ -1349,9 +1343,6 @@
     <t>Carlos Rodríguez</t>
   </si>
   <si>
-    <t>Danny Van Poppel</t>
-  </si>
-  <si>
     <t>Jason Tesson</t>
   </si>
   <si>
@@ -1380,9 +1371,6 @@
   </si>
   <si>
     <t>Marijn Van Den Berg</t>
-  </si>
-  <si>
-    <t>Mathieu Van Der Poel</t>
   </si>
   <si>
     <t>Michael Matthews</t>
@@ -1777,16 +1765,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
   <dimension ref="A1:M118"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1827,7 +1815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1868,7 +1856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1909,7 +1897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1950,7 +1938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1991,7 +1979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2032,7 +2020,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2073,7 +2061,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2114,7 +2102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2155,7 +2143,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2196,7 +2184,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2237,7 +2225,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2278,7 +2266,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2319,7 +2307,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2360,7 +2348,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2401,7 +2389,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2442,7 +2430,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2483,7 +2471,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2524,7 +2512,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2565,7 +2553,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2606,7 +2594,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2647,7 +2635,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2670,7 +2658,7 @@
         <v>90</v>
       </c>
       <c r="H22" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
         <v>119</v>
@@ -2682,13 +2670,13 @@
         <v>116</v>
       </c>
       <c r="L22" t="s">
+        <v>159</v>
+      </c>
+      <c r="M22" t="s">
         <v>160</v>
       </c>
-      <c r="M22" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2708,28 +2696,28 @@
         <v>128</v>
       </c>
       <c r="G23" t="s">
+        <v>162</v>
+      </c>
+      <c r="H23" t="s">
         <v>163</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>164</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>165</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>166</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>167</v>
-      </c>
-      <c r="L23" t="s">
-        <v>168</v>
       </c>
       <c r="M23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2737,7 +2725,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
         <v>130</v>
@@ -2770,7 +2758,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2799,7 +2787,7 @@
         <v>145</v>
       </c>
       <c r="J25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K25" t="s">
         <v>146</v>
@@ -2808,33 +2796,33 @@
         <v>149</v>
       </c>
       <c r="M25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" t="s">
         <v>171</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>172</v>
-      </c>
-      <c r="E26" t="s">
-        <v>173</v>
       </c>
       <c r="F26" t="s">
         <v>77</v>
       </c>
       <c r="G26" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" t="s">
         <v>174</v>
-      </c>
-      <c r="H26" t="s">
-        <v>175</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
@@ -2843,124 +2831,124 @@
         <v>121</v>
       </c>
       <c r="K26" t="s">
+        <v>175</v>
+      </c>
+      <c r="L26" t="s">
         <v>176</v>
-      </c>
-      <c r="L26" t="s">
-        <v>177</v>
       </c>
       <c r="M26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
       <c r="B27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D27" t="s">
         <v>142</v>
       </c>
       <c r="E27" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" t="s">
         <v>179</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>180</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>181</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>182</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>183</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
+        <v>353</v>
+      </c>
+      <c r="L27" t="s">
         <v>184</v>
       </c>
-      <c r="K27" t="s">
+      <c r="M27" t="s">
         <v>185</v>
       </c>
-      <c r="L27" t="s">
-        <v>186</v>
-      </c>
-      <c r="M27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" t="s">
         <v>190</v>
       </c>
-      <c r="E28" t="s">
-        <v>181</v>
-      </c>
-      <c r="F28" t="s">
-        <v>180</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>191</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>192</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" t="s">
         <v>193</v>
       </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>194</v>
       </c>
-      <c r="K28" t="s">
+      <c r="M28" t="s">
         <v>195</v>
       </c>
-      <c r="L28" t="s">
-        <v>196</v>
-      </c>
-      <c r="M28" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F29" t="s">
+        <v>196</v>
+      </c>
+      <c r="G29" t="s">
+        <v>197</v>
+      </c>
+      <c r="H29" t="s">
         <v>198</v>
       </c>
-      <c r="G29" t="s">
-        <v>199</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>200</v>
-      </c>
-      <c r="I29" t="s">
-        <v>202</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
@@ -2975,18 +2963,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -2995,33 +2983,33 @@
         <v>115</v>
       </c>
       <c r="G30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J30" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -3030,13 +3018,13 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" t="s">
+        <v>207</v>
+      </c>
+      <c r="G31" t="s">
         <v>208</v>
-      </c>
-      <c r="F31" t="s">
-        <v>209</v>
-      </c>
-      <c r="G31" t="s">
-        <v>210</v>
       </c>
       <c r="H31" t="s">
         <v>64</v>
@@ -3045,24 +3033,24 @@
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K31" t="s">
+        <v>209</v>
+      </c>
+      <c r="L31" t="s">
+        <v>210</v>
+      </c>
+      <c r="M31" t="s">
         <v>211</v>
       </c>
-      <c r="L31" t="s">
-        <v>212</v>
-      </c>
-      <c r="M31" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -3074,7 +3062,7 @@
         <v>154</v>
       </c>
       <c r="F32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G32" t="s">
         <v>78</v>
@@ -3083,10 +3071,10 @@
         <v>130</v>
       </c>
       <c r="I32" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J32" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K32" t="s">
         <v>109</v>
@@ -3098,18 +3086,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
       <c r="B33" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
         <v>115</v>
@@ -3121,30 +3109,30 @@
         <v>106</v>
       </c>
       <c r="H33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I33" t="s">
         <v>147</v>
       </c>
       <c r="J33" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
       <c r="B34" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
@@ -3162,7 +3150,7 @@
         <v>120</v>
       </c>
       <c r="H34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -3180,59 +3168,59 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
       <c r="B35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
         <v>51</v>
       </c>
       <c r="D35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E35" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" t="s">
         <v>221</v>
       </c>
-      <c r="E35" t="s">
+      <c r="H35" t="s">
         <v>222</v>
-      </c>
-      <c r="F35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" t="s">
-        <v>223</v>
-      </c>
-      <c r="H35" t="s">
-        <v>224</v>
       </c>
       <c r="I35" t="s">
         <v>149</v>
       </c>
       <c r="J35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s">
         <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C36" t="s">
         <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
         <v>89</v>
@@ -3241,16 +3229,16 @@
         <v>106</v>
       </c>
       <c r="G36" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J36" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K36" t="s">
         <v>147</v>
@@ -3262,94 +3250,94 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C37" t="s">
         <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E37" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F37" t="s">
         <v>116</v>
       </c>
       <c r="G37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H37" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J37" t="s">
         <v>149</v>
       </c>
       <c r="K37" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
       <c r="B38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s">
         <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G38" t="s">
         <v>106</v>
       </c>
       <c r="H38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
       </c>
       <c r="J38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
         <v>147</v>
       </c>
       <c r="L38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M38" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
       <c r="B39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C39" t="s">
         <v>158</v>
@@ -3358,16 +3346,16 @@
         <v>116</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I39" t="s">
         <v>37</v>
@@ -3376,27 +3364,27 @@
         <v>149</v>
       </c>
       <c r="K39" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L39" t="s">
         <v>68</v>
       </c>
       <c r="M39" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
       <c r="B40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
         <v>64</v>
@@ -3411,27 +3399,27 @@
         <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J40" t="s">
         <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
       <c r="B41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C41" t="s">
         <v>158</v>
@@ -3443,45 +3431,45 @@
         <v>106</v>
       </c>
       <c r="F41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
         <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I41" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J41" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K41" t="s">
         <v>78</v>
       </c>
       <c r="L41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E42" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F42" t="s">
         <v>116</v>
@@ -3490,33 +3478,33 @@
         <v>149</v>
       </c>
       <c r="H42" t="s">
+        <v>233</v>
+      </c>
+      <c r="I42" t="s">
+        <v>222</v>
+      </c>
+      <c r="J42" t="s">
+        <v>227</v>
+      </c>
+      <c r="K42" t="s">
+        <v>228</v>
+      </c>
+      <c r="L42" t="s">
         <v>235</v>
       </c>
-      <c r="I42" t="s">
-        <v>224</v>
-      </c>
-      <c r="J42" t="s">
-        <v>229</v>
-      </c>
-      <c r="K42" t="s">
-        <v>230</v>
-      </c>
-      <c r="L42" t="s">
-        <v>237</v>
-      </c>
       <c r="M42" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
       <c r="B43" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s">
         <v>130</v>
@@ -3525,7 +3513,7 @@
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G43" t="s">
         <v>128</v>
@@ -3537,7 +3525,7 @@
         <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K43" t="s">
         <v>124</v>
@@ -3546,56 +3534,56 @@
         <v>66</v>
       </c>
       <c r="M43" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
       <c r="B44" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C44" t="s">
         <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E44" t="s">
         <v>106</v>
       </c>
       <c r="F44" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G44" t="s">
         <v>89</v>
       </c>
       <c r="H44" t="s">
+        <v>240</v>
+      </c>
+      <c r="I44" t="s">
+        <v>241</v>
+      </c>
+      <c r="J44" t="s">
         <v>242</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>243</v>
       </c>
-      <c r="J44" t="s">
+      <c r="L44" t="s">
         <v>244</v>
       </c>
-      <c r="K44" t="s">
-        <v>245</v>
-      </c>
-      <c r="L44" t="s">
-        <v>246</v>
-      </c>
       <c r="M44" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
         <v>60</v>
@@ -3607,118 +3595,118 @@
         <v>121</v>
       </c>
       <c r="F45" t="s">
+        <v>246</v>
+      </c>
+      <c r="G45" t="s">
+        <v>247</v>
+      </c>
+      <c r="H45" t="s">
         <v>248</v>
       </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
         <v>249</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>250</v>
       </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>251</v>
       </c>
-      <c r="J45" t="s">
+      <c r="L45" t="s">
         <v>252</v>
       </c>
-      <c r="K45" t="s">
+      <c r="M45" t="s">
         <v>253</v>
       </c>
-      <c r="L45" t="s">
-        <v>254</v>
-      </c>
-      <c r="M45" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C46" t="s">
         <v>60</v>
       </c>
       <c r="D46" t="s">
+        <v>202</v>
+      </c>
+      <c r="E46" t="s">
+        <v>342</v>
+      </c>
+      <c r="F46" t="s">
         <v>204</v>
       </c>
-      <c r="E46" t="s">
-        <v>344</v>
-      </c>
-      <c r="F46" t="s">
-        <v>206</v>
-      </c>
       <c r="G46" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H46" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I46" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M46" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C47" t="s">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E47" t="s">
         <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J47" t="s">
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L47" t="s">
         <v>144</v>
       </c>
       <c r="M47" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
       <c r="B48" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s">
         <v>1</v>
@@ -3727,121 +3715,121 @@
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F48" t="s">
         <v>62</v>
       </c>
       <c r="G48" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H48" t="s">
+        <v>263</v>
+      </c>
+      <c r="I48" t="s">
+        <v>258</v>
+      </c>
+      <c r="J48" t="s">
+        <v>165</v>
+      </c>
+      <c r="K48" t="s">
+        <v>264</v>
+      </c>
+      <c r="L48" t="s">
         <v>265</v>
       </c>
-      <c r="I48" t="s">
-        <v>260</v>
-      </c>
-      <c r="J48" t="s">
-        <v>166</v>
-      </c>
-      <c r="K48" t="s">
+      <c r="M48" t="s">
         <v>266</v>
       </c>
-      <c r="L48" t="s">
-        <v>267</v>
-      </c>
-      <c r="M48" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C49" t="s">
         <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E49" t="s">
         <v>123</v>
       </c>
       <c r="F49" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I49" t="s">
         <v>122</v>
       </c>
       <c r="J49" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K49" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="L49" t="s">
         <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
       <c r="B50" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C50" t="s">
         <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G50" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H50" t="s">
         <v>50</v>
       </c>
       <c r="I50" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J50" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L50" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
       <c r="B51" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -3850,10 +3838,10 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F51" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G51" t="s">
         <v>79</v>
@@ -3862,191 +3850,191 @@
         <v>86</v>
       </c>
       <c r="I51" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J51" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M51" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
       <c r="B52" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C52" t="s">
         <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E52" t="s">
         <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G52" t="s">
         <v>157</v>
       </c>
       <c r="H52" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I52" t="s">
         <v>74</v>
       </c>
       <c r="J52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K52" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L52" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M52" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
       <c r="B53" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F53" t="s">
         <v>77</v>
       </c>
       <c r="G53" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H53" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
       </c>
       <c r="J53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K53" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L53" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
       <c r="B54" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C54" t="s">
         <v>158</v>
       </c>
       <c r="D54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F54" t="s">
         <v>157</v>
       </c>
       <c r="G54" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H54" t="s">
         <v>74</v>
       </c>
       <c r="I54" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J54" t="s">
         <v>117</v>
       </c>
       <c r="K54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L54" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M54" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
       <c r="B55" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D55" t="s">
         <v>52</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F55" t="s">
         <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I55" t="s">
+        <v>282</v>
+      </c>
+      <c r="J55" t="s">
+        <v>283</v>
+      </c>
+      <c r="K55" t="s">
+        <v>259</v>
+      </c>
+      <c r="L55" t="s">
+        <v>179</v>
+      </c>
+      <c r="M55" t="s">
         <v>284</v>
       </c>
-      <c r="J55" t="s">
-        <v>285</v>
-      </c>
-      <c r="K55" t="s">
-        <v>261</v>
-      </c>
-      <c r="L55" t="s">
-        <v>180</v>
-      </c>
-      <c r="M55" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C56" t="s">
         <v>60</v>
@@ -4058,36 +4046,36 @@
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G56" t="s">
         <v>124</v>
       </c>
       <c r="H56" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I56" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L56" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M56" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
       <c r="B57" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C57" t="s">
         <v>60</v>
@@ -4096,10 +4084,10 @@
         <v>152</v>
       </c>
       <c r="E57" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F57" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G57" t="s">
         <v>64</v>
@@ -4108,109 +4096,109 @@
         <v>37</v>
       </c>
       <c r="I57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K57" t="s">
         <v>123</v>
       </c>
       <c r="L57" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M57" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
       <c r="B58" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C58" t="s">
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F58" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G58" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
       </c>
       <c r="I58" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J58" t="s">
         <v>105</v>
       </c>
       <c r="K58" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M58" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
       <c r="B59" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C59" t="s">
         <v>60</v>
       </c>
       <c r="D59" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F59" t="s">
         <v>74</v>
       </c>
       <c r="G59" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I59" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J59" t="s">
         <v>77</v>
       </c>
       <c r="K59" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M59" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
       <c r="B60" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4225,7 +4213,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H60" t="s">
         <v>103</v>
@@ -4240,18 +4228,18 @@
         <v>79</v>
       </c>
       <c r="L60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M60" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
       <c r="B61" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -4260,48 +4248,48 @@
         <v>142</v>
       </c>
       <c r="E61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F61" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H61" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I61" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J61" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K61" t="s">
         <v>157</v>
       </c>
       <c r="L61" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
       <c r="B62" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C62" t="s">
         <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -4313,109 +4301,109 @@
         <v>106</v>
       </c>
       <c r="I62" t="s">
+        <v>298</v>
+      </c>
+      <c r="J62" t="s">
+        <v>299</v>
+      </c>
+      <c r="K62" t="s">
+        <v>243</v>
+      </c>
+      <c r="L62" t="s">
         <v>300</v>
       </c>
-      <c r="J62" t="s">
+      <c r="M62" t="s">
         <v>301</v>
       </c>
-      <c r="K62" t="s">
-        <v>245</v>
-      </c>
-      <c r="L62" t="s">
-        <v>302</v>
-      </c>
-      <c r="M62" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
       <c r="B63" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C63" t="s">
         <v>60</v>
       </c>
       <c r="D63" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E63" t="s">
         <v>122</v>
       </c>
       <c r="F63" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G63" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H63" t="s">
         <v>47</v>
       </c>
       <c r="I63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J63" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K63" t="s">
         <v>123</v>
       </c>
       <c r="L63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M63" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
       <c r="B64" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C64" t="s">
         <v>51</v>
       </c>
       <c r="D64" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E64" t="s">
         <v>106</v>
       </c>
       <c r="F64" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G64" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H64" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I64" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J64" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K64" t="s">
         <v>142</v>
       </c>
       <c r="L64" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M64" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
       <c r="B65" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C65" t="s">
         <v>55</v>
@@ -4427,13 +4415,13 @@
         <v>157</v>
       </c>
       <c r="F65" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G65" t="s">
         <v>149</v>
       </c>
       <c r="H65" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I65" t="s">
         <v>116</v>
@@ -4442,21 +4430,21 @@
         <v>106</v>
       </c>
       <c r="K65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L65" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M65" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
       <c r="B66" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C66" t="s">
         <v>158</v>
@@ -4468,16 +4456,16 @@
         <v>93</v>
       </c>
       <c r="F66" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G66" t="s">
         <v>61</v>
       </c>
       <c r="H66" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I66" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J66" t="s">
         <v>56</v>
@@ -4486,100 +4474,100 @@
         <v>106</v>
       </c>
       <c r="L66" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M66" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
       <c r="B67" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C67" t="s">
         <v>60</v>
       </c>
       <c r="D67" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E67" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F67" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I67" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J67" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K67" t="s">
         <v>113</v>
       </c>
       <c r="L67" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M67" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
       <c r="B68" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C68" t="s">
         <v>60</v>
       </c>
       <c r="D68" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F68" t="s">
+        <v>311</v>
+      </c>
+      <c r="G68" t="s">
+        <v>188</v>
+      </c>
+      <c r="H68" t="s">
+        <v>312</v>
+      </c>
+      <c r="I68" t="s">
         <v>313</v>
       </c>
-      <c r="G68" t="s">
-        <v>190</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="J68" t="s">
         <v>314</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>315</v>
-      </c>
-      <c r="J68" t="s">
-        <v>316</v>
-      </c>
-      <c r="K68" t="s">
-        <v>317</v>
       </c>
       <c r="L68" t="s">
         <v>52</v>
       </c>
       <c r="M68" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
       <c r="B69" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C69" t="s">
         <v>60</v>
@@ -4588,80 +4576,80 @@
         <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F69" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G69" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H69" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I69" t="s">
         <v>27</v>
       </c>
       <c r="J69" t="s">
+        <v>324</v>
+      </c>
+      <c r="K69" t="s">
+        <v>325</v>
+      </c>
+      <c r="L69" t="s">
         <v>326</v>
       </c>
-      <c r="K69" t="s">
+      <c r="M69" t="s">
         <v>327</v>
       </c>
-      <c r="L69" t="s">
-        <v>328</v>
-      </c>
-      <c r="M69" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
       <c r="B70" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C70" t="s">
         <v>0</v>
       </c>
       <c r="D70" t="s">
+        <v>329</v>
+      </c>
+      <c r="E70" t="s">
+        <v>342</v>
+      </c>
+      <c r="F70" t="s">
+        <v>330</v>
+      </c>
+      <c r="G70" t="s">
         <v>331</v>
       </c>
-      <c r="E70" t="s">
-        <v>344</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="H70" t="s">
         <v>332</v>
       </c>
-      <c r="G70" t="s">
+      <c r="I70" t="s">
         <v>333</v>
       </c>
-      <c r="H70" t="s">
+      <c r="J70" t="s">
         <v>334</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>335</v>
       </c>
-      <c r="J70" t="s">
+      <c r="L70" t="s">
         <v>336</v>
-      </c>
-      <c r="K70" t="s">
-        <v>337</v>
-      </c>
-      <c r="L70" t="s">
-        <v>338</v>
       </c>
       <c r="M70" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
       <c r="B71" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C71" t="s">
         <v>1</v>
@@ -4673,36 +4661,36 @@
         <v>154</v>
       </c>
       <c r="F71" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G71" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H71" t="s">
         <v>68</v>
       </c>
       <c r="I71" t="s">
+        <v>338</v>
+      </c>
+      <c r="J71" t="s">
+        <v>228</v>
+      </c>
+      <c r="K71" t="s">
+        <v>339</v>
+      </c>
+      <c r="L71" t="s">
         <v>340</v>
       </c>
-      <c r="J71" t="s">
-        <v>230</v>
-      </c>
-      <c r="K71" t="s">
-        <v>341</v>
-      </c>
-      <c r="L71" t="s">
-        <v>342</v>
-      </c>
       <c r="M71" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
       <c r="B72" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C72" t="s">
         <v>60</v>
@@ -4714,92 +4702,92 @@
         <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G72" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I72" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L72" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
       <c r="B73" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C73" t="s">
         <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E73" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G73" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H73" t="s">
         <v>68</v>
       </c>
       <c r="I73" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J73" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K73" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L73" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M73" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
       <c r="B74" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C74" t="s">
         <v>51</v>
       </c>
       <c r="D74" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E74" t="s">
         <v>32</v>
       </c>
       <c r="F74" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G74" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H74" t="s">
         <v>154</v>
@@ -4808,24 +4796,24 @@
         <v>68</v>
       </c>
       <c r="J74" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K74" t="s">
+        <v>345</v>
+      </c>
+      <c r="L74" t="s">
         <v>347</v>
       </c>
-      <c r="L74" t="s">
-        <v>349</v>
-      </c>
       <c r="M74" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
       <c r="B75" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C75" t="s">
         <v>55</v>
@@ -4834,45 +4822,45 @@
         <v>89</v>
       </c>
       <c r="E75" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F75" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G75" t="s">
         <v>154</v>
       </c>
       <c r="H75" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I75" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J75" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K75" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L75" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M75" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
       <c r="B76" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C76" t="s">
         <v>60</v>
       </c>
       <c r="D76" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E76" t="s">
         <v>142</v>
@@ -4881,19 +4869,19 @@
         <v>74</v>
       </c>
       <c r="G76" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H76" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I76" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J76" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K76" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L76" t="s">
         <v>106</v>
@@ -4902,39 +4890,39 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E77" t="s">
         <v>153</v>
       </c>
       <c r="F77" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I77" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J77" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K77" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L77" t="s">
         <v>48</v>
@@ -4943,258 +4931,258 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
       <c r="B78" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C78" t="s">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E78" t="s">
         <v>157</v>
       </c>
       <c r="F78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G78" t="s">
         <v>119</v>
       </c>
       <c r="H78" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I78" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J78" t="s">
         <v>90</v>
       </c>
       <c r="K78" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L78" t="s">
         <v>111</v>
       </c>
       <c r="M78" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
       <c r="B79" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C79" t="s">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E79" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F79" t="s">
         <v>48</v>
       </c>
       <c r="G79" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H79" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I79" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J79" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K79" t="s">
         <v>148</v>
       </c>
       <c r="L79" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M79" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
       <c r="B80" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C80" t="s">
         <v>43</v>
       </c>
       <c r="D80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E80" t="s">
         <v>48</v>
       </c>
       <c r="F80" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G80" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H80" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I80" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J80" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K80" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L80" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="M80" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
       <c r="B81" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C81" t="s">
         <v>60</v>
       </c>
       <c r="D81" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E81" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F81" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G81" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H81" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I81" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J81" t="s">
         <v>30</v>
       </c>
       <c r="K81" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L81" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M81" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
       <c r="B82" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C82" t="s">
         <v>51</v>
       </c>
       <c r="D82" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E82" t="s">
         <v>157</v>
       </c>
       <c r="F82" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G82" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H82" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I82" t="s">
         <v>148</v>
       </c>
       <c r="J82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K82" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L82" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M82" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
       <c r="B83" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C83" t="s">
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E83" t="s">
         <v>157</v>
       </c>
       <c r="F83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G83" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H83" t="s">
         <v>119</v>
       </c>
       <c r="I83" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J83" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K83" t="s">
         <v>148</v>
       </c>
       <c r="L83" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M83" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
       <c r="B84" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C84" t="s">
         <v>0</v>
@@ -5221,36 +5209,36 @@
         <v>125</v>
       </c>
       <c r="K84" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="L84" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M84" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
       <c r="B85" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C85" t="s">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E85" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F85" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G85" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H85" t="s">
         <v>89</v>
@@ -5259,24 +5247,24 @@
         <v>32</v>
       </c>
       <c r="J85" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L85" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M85" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
       <c r="B86" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C86" t="s">
         <v>43</v>
@@ -5288,7 +5276,7 @@
         <v>130</v>
       </c>
       <c r="F86" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G86" t="s">
         <v>136</v>
@@ -5303,21 +5291,21 @@
         <v>125</v>
       </c>
       <c r="K86" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L86" t="s">
         <v>15</v>
       </c>
       <c r="M86" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
       <c r="B87" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C87" t="s">
         <v>51</v>
@@ -5326,10 +5314,10 @@
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F87" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G87" t="s">
         <v>76</v>
@@ -5338,77 +5326,77 @@
         <v>147</v>
       </c>
       <c r="I87" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J87" t="s">
         <v>105</v>
       </c>
       <c r="K87" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="L87" t="s">
         <v>54</v>
       </c>
       <c r="M87" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
       <c r="B88" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C88" t="s">
         <v>55</v>
       </c>
       <c r="D88" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E88" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F88" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G88" t="s">
+        <v>369</v>
+      </c>
+      <c r="H88" t="s">
+        <v>192</v>
+      </c>
+      <c r="I88" t="s">
+        <v>370</v>
+      </c>
+      <c r="J88" t="s">
         <v>371</v>
       </c>
-      <c r="H88" t="s">
-        <v>194</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="K88" t="s">
         <v>372</v>
-      </c>
-      <c r="J88" t="s">
-        <v>373</v>
-      </c>
-      <c r="K88" t="s">
-        <v>374</v>
       </c>
       <c r="L88" t="s">
         <v>54</v>
       </c>
       <c r="M88" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
       <c r="B89" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C89" t="s">
         <v>158</v>
       </c>
       <c r="D89" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F89" t="s">
         <v>120</v>
@@ -5420,153 +5408,153 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K89" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L89" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M89" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
       <c r="B90" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C90" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D90" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E90" t="s">
         <v>117</v>
       </c>
       <c r="F90" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G90" t="s">
         <v>89</v>
       </c>
       <c r="H90" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J90" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K90" t="s">
         <v>118</v>
       </c>
       <c r="L90" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M90" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
       <c r="B91" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C91" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F91" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G91" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H91" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J91" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="K91" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L91" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M91" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
       <c r="B92" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C92" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D92" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E92" t="s">
         <v>117</v>
       </c>
       <c r="F92" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G92" t="s">
         <v>154</v>
       </c>
       <c r="H92" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I92" t="s">
         <v>118</v>
       </c>
       <c r="J92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K92" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L92" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M92" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C93" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D93" t="s">
         <v>152</v>
@@ -5578,95 +5566,95 @@
         <v>108</v>
       </c>
       <c r="G93" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H93" t="s">
         <v>118</v>
       </c>
       <c r="I93" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J93" t="s">
+        <v>381</v>
+      </c>
+      <c r="K93" t="s">
+        <v>382</v>
+      </c>
+      <c r="L93" t="s">
+        <v>369</v>
+      </c>
+      <c r="M93" t="s">
         <v>383</v>
       </c>
-      <c r="K93" t="s">
-        <v>384</v>
-      </c>
-      <c r="L93" t="s">
-        <v>371</v>
-      </c>
-      <c r="M93" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
       <c r="B94" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C94" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F94" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G94" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H94" t="s">
         <v>68</v>
       </c>
       <c r="I94" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K94" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L94" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
       <c r="B95" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C95" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D95" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E95" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F95" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G95" t="s">
         <v>19</v>
       </c>
       <c r="H95" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I95" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J95" t="s">
         <v>136</v>
@@ -5678,71 +5666,71 @@
         <v>53</v>
       </c>
       <c r="M95" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
       <c r="B96" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C96" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D96" t="s">
+        <v>391</v>
+      </c>
+      <c r="E96" t="s">
+        <v>364</v>
+      </c>
+      <c r="F96" t="s">
+        <v>234</v>
+      </c>
+      <c r="G96" t="s">
+        <v>229</v>
+      </c>
+      <c r="H96" t="s">
+        <v>392</v>
+      </c>
+      <c r="I96" t="s">
         <v>393</v>
       </c>
-      <c r="E96" t="s">
-        <v>366</v>
-      </c>
-      <c r="F96" t="s">
-        <v>236</v>
-      </c>
-      <c r="G96" t="s">
-        <v>231</v>
-      </c>
-      <c r="H96" t="s">
-        <v>394</v>
-      </c>
-      <c r="I96" t="s">
-        <v>395</v>
-      </c>
       <c r="J96" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="K96" t="s">
         <v>62</v>
       </c>
       <c r="L96" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M96" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
       <c r="B97" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C97" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E97" t="s">
         <v>117</v>
       </c>
       <c r="F97" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G97" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H97" t="s">
         <v>89</v>
@@ -5751,45 +5739,45 @@
         <v>154</v>
       </c>
       <c r="J97" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K97" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L97" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M97" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
       <c r="B98" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C98" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D98" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E98" t="s">
         <v>87</v>
       </c>
       <c r="F98" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G98" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H98" t="s">
         <v>120</v>
       </c>
       <c r="I98" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J98" t="s">
         <v>15</v>
@@ -5798,30 +5786,30 @@
         <v>19</v>
       </c>
       <c r="L98" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M98" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
       <c r="B99" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C99" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D99" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E99" t="s">
         <v>117</v>
       </c>
       <c r="F99" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G99" t="s">
         <v>154</v>
@@ -5830,71 +5818,71 @@
         <v>118</v>
       </c>
       <c r="I99" t="s">
+        <v>182</v>
+      </c>
+      <c r="J99" t="s">
         <v>183</v>
       </c>
-      <c r="J99" t="s">
-        <v>184</v>
-      </c>
       <c r="K99" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L99" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M99" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
       <c r="B100" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C100" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E100" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F100" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G100" t="s">
         <v>68</v>
       </c>
       <c r="H100" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="I100" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J100" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K100" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L100" t="s">
         <v>26</v>
       </c>
       <c r="M100" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
       <c r="B101" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C101" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -5909,83 +5897,83 @@
         <v>62</v>
       </c>
       <c r="H101" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I101" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J101" t="s">
         <v>136</v>
       </c>
       <c r="K101" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L101" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M101" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
       <c r="B102" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C102" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D102" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E102" t="s">
         <v>118</v>
       </c>
       <c r="F102" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G102" t="s">
         <v>117</v>
       </c>
       <c r="H102" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I102" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J102" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L102" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M102" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
       <c r="B103" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C103" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E103" t="s">
         <v>117</v>
       </c>
       <c r="F103" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G103" t="s">
         <v>118</v>
@@ -5994,30 +5982,30 @@
         <v>154</v>
       </c>
       <c r="I103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J103" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K103" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M103" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
       <c r="B104" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C104" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D104" t="s">
         <v>130</v>
@@ -6026,10 +6014,10 @@
         <v>66</v>
       </c>
       <c r="F104" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G104" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H104" t="s">
         <v>136</v>
@@ -6041,21 +6029,21 @@
         <v>15</v>
       </c>
       <c r="K104" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L104" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
       <c r="B105" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
         <v>60</v>
@@ -6064,66 +6052,66 @@
         <v>121</v>
       </c>
       <c r="E105" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F105" t="s">
         <v>64</v>
       </c>
       <c r="G105" t="s">
+        <v>411</v>
+      </c>
+      <c r="H105" t="s">
+        <v>412</v>
+      </c>
+      <c r="I105" t="s">
         <v>413</v>
       </c>
-      <c r="H105" t="s">
-        <v>414</v>
-      </c>
-      <c r="I105" t="s">
-        <v>415</v>
-      </c>
       <c r="J105" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K105" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L105" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M105" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
       <c r="B106" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E106" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F106" t="s">
+        <v>415</v>
+      </c>
+      <c r="G106" t="s">
+        <v>416</v>
+      </c>
+      <c r="H106" t="s">
         <v>417</v>
       </c>
-      <c r="G106" t="s">
-        <v>418</v>
-      </c>
-      <c r="H106" t="s">
-        <v>419</v>
-      </c>
       <c r="I106" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J106" t="s">
         <v>111</v>
       </c>
       <c r="K106" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L106" t="s">
         <v>149</v>
@@ -6132,12 +6120,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
       <c r="B107" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C107" t="s">
         <v>1</v>
@@ -6146,54 +6134,54 @@
         <v>50</v>
       </c>
       <c r="E107" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F107" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G107" t="s">
         <v>93</v>
       </c>
       <c r="H107" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I107" t="s">
+        <v>421</v>
+      </c>
+      <c r="J107" t="s">
+        <v>422</v>
+      </c>
+      <c r="K107" t="s">
         <v>423</v>
-      </c>
-      <c r="J107" t="s">
-        <v>424</v>
-      </c>
-      <c r="K107" t="s">
-        <v>425</v>
       </c>
       <c r="L107" t="s">
         <v>48</v>
       </c>
       <c r="M107" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
       <c r="B108" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C108" t="s">
         <v>51</v>
       </c>
       <c r="D108" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E108" t="s">
         <v>48</v>
       </c>
       <c r="F108" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G108" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H108" t="s">
         <v>93</v>
@@ -6202,80 +6190,80 @@
         <v>28</v>
       </c>
       <c r="J108" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K108" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="L108" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="M108" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
       <c r="B109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C109" t="s">
         <v>55</v>
       </c>
       <c r="D109" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F109" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G109" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H109" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I109" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K109" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L109" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="M109" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
       <c r="B110" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C110" t="s">
         <v>158</v>
       </c>
       <c r="D110" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E110" t="s">
         <v>106</v>
       </c>
       <c r="F110" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G110" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H110" t="s">
         <v>93</v>
@@ -6284,30 +6272,30 @@
         <v>148</v>
       </c>
       <c r="J110" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K110" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L110" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M110" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
       <c r="B111" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C111" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D111" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E111" t="s">
         <v>143</v>
@@ -6316,39 +6304,39 @@
         <v>106</v>
       </c>
       <c r="G111" t="s">
+        <v>180</v>
+      </c>
+      <c r="H111" t="s">
+        <v>240</v>
+      </c>
+      <c r="I111" t="s">
         <v>181</v>
-      </c>
-      <c r="H111" t="s">
-        <v>242</v>
-      </c>
-      <c r="I111" t="s">
-        <v>182</v>
       </c>
       <c r="J111" t="s">
         <v>142</v>
       </c>
       <c r="K111" t="s">
+        <v>430</v>
+      </c>
+      <c r="L111" t="s">
         <v>432</v>
       </c>
-      <c r="L111" t="s">
-        <v>434</v>
-      </c>
       <c r="M111" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
       <c r="B112" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C112" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D112" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E112" t="s">
         <v>143</v>
@@ -6357,33 +6345,33 @@
         <v>106</v>
       </c>
       <c r="G112" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H112" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I112" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J112" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K112" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L112" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M112" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
       <c r="B113" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C113" t="s">
         <v>60</v>
@@ -6398,42 +6386,42 @@
         <v>17</v>
       </c>
       <c r="G113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H113" t="s">
-        <v>436</v>
+        <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J113" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K113" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L113" t="s">
         <v>114</v>
       </c>
       <c r="M113" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C114" t="s">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E114" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F114" t="s">
         <v>58</v>
@@ -6448,7 +6436,7 @@
         <v>79</v>
       </c>
       <c r="J114" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K114" t="s">
         <v>80</v>
@@ -6460,53 +6448,53 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
       <c r="B115" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C115" t="s">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E115" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F115" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G115" t="s">
         <v>29</v>
       </c>
       <c r="H115" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="I115" t="s">
         <v>75</v>
       </c>
       <c r="J115" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K115" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L115" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M115" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
       <c r="B116" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C116" t="s">
         <v>43</v>
@@ -6515,63 +6503,63 @@
         <v>26</v>
       </c>
       <c r="E116" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F116" t="s">
         <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H116" t="s">
-        <v>447</v>
+        <v>171</v>
       </c>
       <c r="I116" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J116" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K116" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="L116" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="M116" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
       <c r="B117" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C117" t="s">
         <v>51</v>
       </c>
       <c r="D117" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E117" t="s">
-        <v>447</v>
+        <v>171</v>
       </c>
       <c r="F117" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G117" t="s">
         <v>75</v>
       </c>
       <c r="H117" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="I117" t="s">
         <v>80</v>
       </c>
       <c r="J117" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="K117" t="s">
         <v>27</v>
@@ -6583,45 +6571,45 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
       <c r="B118" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C118" t="s">
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E118" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F118" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G118" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H118" t="s">
         <v>145</v>
       </c>
       <c r="I118" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J118" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K118" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L118" t="s">
         <v>103</v>
       </c>
       <c r="M118" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/html league/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2138BF29-1984-41BD-96D5-9B4F146DFFCC}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13529FC0-5827-4921-93A7-6460AA385E1A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="453">
   <si>
     <t>Stage 1</t>
   </si>
@@ -443,7 +443,7 @@
     <t>Daniel Skerl</t>
   </si>
   <si>
-    <t>Steffen De Schuyteneer</t>
+    <t>Steffen De Schuyteneere</t>
   </si>
   <si>
     <t>Axel Huens</t>
@@ -518,6 +518,9 @@
     <t>Stage 6</t>
   </si>
   <si>
+    <t>T. H. Johannessen</t>
+  </si>
+  <si>
     <t>David Gaudu</t>
   </si>
   <si>
@@ -593,6 +596,9 @@
     <t>Egan Bernal</t>
   </si>
   <si>
+    <t>Jefferson Cepeda</t>
+  </si>
+  <si>
     <t>Igor Arrieta</t>
   </si>
   <si>
@@ -1343,6 +1349,9 @@
     <t>Carlos Rodríguez</t>
   </si>
   <si>
+    <t>Danny Van Poppel</t>
+  </si>
+  <si>
     <t>Jason Tesson</t>
   </si>
   <si>
@@ -1371,6 +1380,9 @@
   </si>
   <si>
     <t>Marijn Van Den Berg</t>
+  </si>
+  <si>
+    <t>Mathieu Van Der Poel</t>
   </si>
   <si>
     <t>Michael Matthews</t>
@@ -1765,16 +1777,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
   <dimension ref="A1:M118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1815,7 +1827,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1856,7 +1868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1897,7 +1909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1938,7 +1950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1979,7 +1991,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2020,7 +2032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2061,7 +2073,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2102,7 +2114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2143,7 +2155,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2184,7 +2196,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2225,7 +2237,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2266,7 +2278,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2307,7 +2319,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2348,7 +2360,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2389,7 +2401,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2430,7 +2442,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2471,7 +2483,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2512,7 +2524,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2553,7 +2565,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2594,7 +2606,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2635,7 +2647,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2658,7 +2670,7 @@
         <v>90</v>
       </c>
       <c r="H22" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="I22" t="s">
         <v>119</v>
@@ -2670,13 +2682,13 @@
         <v>116</v>
       </c>
       <c r="L22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M22" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2696,28 +2708,28 @@
         <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2725,7 +2737,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
         <v>130</v>
@@ -2758,7 +2770,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2787,7 +2799,7 @@
         <v>145</v>
       </c>
       <c r="J25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K25" t="s">
         <v>146</v>
@@ -2796,33 +2808,33 @@
         <v>149</v>
       </c>
       <c r="M25" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F26" t="s">
         <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
@@ -2831,124 +2843,124 @@
         <v>121</v>
       </c>
       <c r="K26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
         <v>142</v>
       </c>
       <c r="E27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G27" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K27" t="s">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="L27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" t="s">
         <v>180</v>
       </c>
-      <c r="F28" t="s">
-        <v>179</v>
-      </c>
       <c r="G28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K28" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M28" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F29" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I29" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
@@ -2963,18 +2975,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E30" t="s">
         <v>142</v>
@@ -2983,33 +2995,33 @@
         <v>115</v>
       </c>
       <c r="G30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J30" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -3018,13 +3030,13 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F31" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H31" t="s">
         <v>64</v>
@@ -3033,24 +3045,24 @@
         <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M31" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
       <c r="B32" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -3062,7 +3074,7 @@
         <v>154</v>
       </c>
       <c r="F32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G32" t="s">
         <v>78</v>
@@ -3071,10 +3083,10 @@
         <v>130</v>
       </c>
       <c r="I32" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J32" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
         <v>109</v>
@@ -3086,18 +3098,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
         <v>115</v>
@@ -3109,30 +3121,30 @@
         <v>106</v>
       </c>
       <c r="H33" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I33" t="s">
         <v>147</v>
       </c>
       <c r="J33" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
       <c r="B34" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C34" t="s">
         <v>43</v>
@@ -3150,7 +3162,7 @@
         <v>120</v>
       </c>
       <c r="H34" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -3168,59 +3180,59 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
       <c r="B35" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
         <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I35" t="s">
         <v>149</v>
       </c>
       <c r="J35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s">
         <v>41</v>
       </c>
       <c r="M35" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
         <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
         <v>89</v>
@@ -3229,16 +3241,16 @@
         <v>106</v>
       </c>
       <c r="G36" t="s">
+        <v>220</v>
+      </c>
+      <c r="H36" t="s">
+        <v>206</v>
+      </c>
+      <c r="I36" t="s">
+        <v>227</v>
+      </c>
+      <c r="J36" t="s">
         <v>218</v>
-      </c>
-      <c r="H36" t="s">
-        <v>204</v>
-      </c>
-      <c r="I36" t="s">
-        <v>225</v>
-      </c>
-      <c r="J36" t="s">
-        <v>216</v>
       </c>
       <c r="K36" t="s">
         <v>147</v>
@@ -3250,94 +3262,94 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
       <c r="B37" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
         <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F37" t="s">
         <v>116</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J37" t="s">
         <v>149</v>
       </c>
       <c r="K37" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L37" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
         <v>55</v>
       </c>
       <c r="D38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E38" t="s">
         <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G38" t="s">
         <v>106</v>
       </c>
       <c r="H38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I38" t="s">
         <v>89</v>
       </c>
       <c r="J38" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K38" t="s">
         <v>147</v>
       </c>
       <c r="L38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M38" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s">
         <v>158</v>
@@ -3346,16 +3358,16 @@
         <v>116</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G39" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I39" t="s">
         <v>37</v>
@@ -3364,27 +3376,27 @@
         <v>149</v>
       </c>
       <c r="K39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L39" t="s">
         <v>68</v>
       </c>
       <c r="M39" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
       <c r="B40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E40" t="s">
         <v>64</v>
@@ -3399,27 +3411,27 @@
         <v>24</v>
       </c>
       <c r="I40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J40" t="s">
         <v>41</v>
       </c>
       <c r="K40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C41" t="s">
         <v>158</v>
@@ -3431,45 +3443,45 @@
         <v>106</v>
       </c>
       <c r="F41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G41" t="s">
         <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K41" t="s">
         <v>78</v>
       </c>
       <c r="L41" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F42" t="s">
         <v>116</v>
@@ -3478,33 +3490,33 @@
         <v>149</v>
       </c>
       <c r="H42" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I42" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D43" t="s">
         <v>130</v>
@@ -3513,7 +3525,7 @@
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G43" t="s">
         <v>128</v>
@@ -3525,7 +3537,7 @@
         <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K43" t="s">
         <v>124</v>
@@ -3534,56 +3546,56 @@
         <v>66</v>
       </c>
       <c r="M43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C44" t="s">
         <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E44" t="s">
         <v>106</v>
       </c>
       <c r="F44" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G44" t="s">
         <v>89</v>
       </c>
       <c r="H44" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K44" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M44" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
       <c r="B45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C45" t="s">
         <v>60</v>
@@ -3595,118 +3607,118 @@
         <v>121</v>
       </c>
       <c r="F45" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G45" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L45" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
       <c r="B46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C46" t="s">
         <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E46" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I46" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J46" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M46" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
       <c r="B47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C47" t="s">
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E47" t="s">
         <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J47" t="s">
         <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L47" t="s">
         <v>144</v>
       </c>
       <c r="M47" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C48" t="s">
         <v>1</v>
@@ -3715,121 +3727,121 @@
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F48" t="s">
         <v>62</v>
       </c>
       <c r="G48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I48" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L48" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M48" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
       <c r="B49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C49" t="s">
         <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E49" t="s">
         <v>123</v>
       </c>
       <c r="F49" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G49" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" t="s">
         <v>122</v>
       </c>
       <c r="J49" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K49" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L49" t="s">
         <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
       <c r="B50" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C50" t="s">
         <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H50" t="s">
         <v>50</v>
       </c>
       <c r="I50" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J50" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M50" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
       <c r="B51" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C51" t="s">
         <v>51</v>
@@ -3838,10 +3850,10 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F51" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G51" t="s">
         <v>79</v>
@@ -3850,191 +3862,191 @@
         <v>86</v>
       </c>
       <c r="I51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J51" t="s">
+        <v>276</v>
+      </c>
+      <c r="K51" t="s">
+        <v>265</v>
+      </c>
+      <c r="L51" t="s">
+        <v>166</v>
+      </c>
+      <c r="M51" t="s">
         <v>274</v>
       </c>
-      <c r="K51" t="s">
-        <v>263</v>
-      </c>
-      <c r="L51" t="s">
-        <v>165</v>
-      </c>
-      <c r="M51" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
       <c r="B52" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C52" t="s">
         <v>55</v>
       </c>
       <c r="D52" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E52" t="s">
         <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
         <v>157</v>
       </c>
       <c r="H52" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I52" t="s">
         <v>74</v>
       </c>
       <c r="J52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M52" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
       <c r="B53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E53" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F53" t="s">
         <v>77</v>
       </c>
       <c r="G53" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H53" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
       </c>
       <c r="J53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K53" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L53" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M53" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C54" t="s">
         <v>158</v>
       </c>
       <c r="D54" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F54" t="s">
         <v>157</v>
       </c>
       <c r="G54" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H54" t="s">
         <v>74</v>
       </c>
       <c r="I54" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J54" t="s">
         <v>117</v>
       </c>
       <c r="K54" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L54" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M54" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
       <c r="B55" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" t="s">
         <v>52</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F55" t="s">
         <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H55" t="s">
+        <v>263</v>
+      </c>
+      <c r="I55" t="s">
+        <v>284</v>
+      </c>
+      <c r="J55" t="s">
+        <v>285</v>
+      </c>
+      <c r="K55" t="s">
         <v>261</v>
       </c>
-      <c r="I55" t="s">
-        <v>282</v>
-      </c>
-      <c r="J55" t="s">
-        <v>283</v>
-      </c>
-      <c r="K55" t="s">
-        <v>259</v>
-      </c>
       <c r="L55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M55" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
       <c r="B56" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C56" t="s">
         <v>60</v>
@@ -4046,36 +4058,36 @@
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G56" t="s">
         <v>124</v>
       </c>
       <c r="H56" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I56" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K56" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L56" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M56" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
       <c r="B57" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C57" t="s">
         <v>60</v>
@@ -4084,10 +4096,10 @@
         <v>152</v>
       </c>
       <c r="E57" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F57" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G57" t="s">
         <v>64</v>
@@ -4096,109 +4108,109 @@
         <v>37</v>
       </c>
       <c r="I57" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K57" t="s">
         <v>123</v>
       </c>
       <c r="L57" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M57" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
       <c r="B58" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C58" t="s">
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H58" t="s">
         <v>58</v>
       </c>
       <c r="I58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J58" t="s">
         <v>105</v>
       </c>
       <c r="K58" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L58" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M58" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
       <c r="B59" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C59" t="s">
         <v>60</v>
       </c>
       <c r="D59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F59" t="s">
         <v>74</v>
       </c>
       <c r="G59" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H59" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J59" t="s">
         <v>77</v>
       </c>
       <c r="K59" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M59" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
@@ -4213,7 +4225,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H60" t="s">
         <v>103</v>
@@ -4228,18 +4240,18 @@
         <v>79</v>
       </c>
       <c r="L60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M60" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
       <c r="B61" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -4248,48 +4260,48 @@
         <v>142</v>
       </c>
       <c r="E61" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F61" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G61" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H61" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I61" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J61" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K61" t="s">
         <v>157</v>
       </c>
       <c r="L61" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M61" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
       <c r="B62" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C62" t="s">
         <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E62" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -4301,109 +4313,109 @@
         <v>106</v>
       </c>
       <c r="I62" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J62" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K62" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L62" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
       <c r="B63" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C63" t="s">
         <v>60</v>
       </c>
       <c r="D63" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E63" t="s">
         <v>122</v>
       </c>
       <c r="F63" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G63" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H63" t="s">
         <v>47</v>
       </c>
       <c r="I63" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J63" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K63" t="s">
         <v>123</v>
       </c>
       <c r="L63" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M63" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
       <c r="B64" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C64" t="s">
         <v>51</v>
       </c>
       <c r="D64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E64" t="s">
         <v>106</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I64" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J64" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K64" t="s">
         <v>142</v>
       </c>
       <c r="L64" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M64" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
       <c r="B65" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C65" t="s">
         <v>55</v>
@@ -4415,13 +4427,13 @@
         <v>157</v>
       </c>
       <c r="F65" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G65" t="s">
         <v>149</v>
       </c>
       <c r="H65" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I65" t="s">
         <v>116</v>
@@ -4430,21 +4442,21 @@
         <v>106</v>
       </c>
       <c r="K65" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L65" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M65" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
       <c r="B66" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C66" t="s">
         <v>158</v>
@@ -4456,16 +4468,16 @@
         <v>93</v>
       </c>
       <c r="F66" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G66" t="s">
         <v>61</v>
       </c>
       <c r="H66" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I66" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J66" t="s">
         <v>56</v>
@@ -4474,100 +4486,100 @@
         <v>106</v>
       </c>
       <c r="L66" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M66" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
       <c r="B67" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C67" t="s">
         <v>60</v>
       </c>
       <c r="D67" t="s">
+        <v>206</v>
+      </c>
+      <c r="E67" t="s">
         <v>204</v>
       </c>
-      <c r="E67" t="s">
-        <v>202</v>
-      </c>
       <c r="F67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J67" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K67" t="s">
         <v>113</v>
       </c>
       <c r="L67" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
       <c r="B68" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C68" t="s">
         <v>60</v>
       </c>
       <c r="D68" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E68" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F68" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H68" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I68" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J68" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K68" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L68" t="s">
         <v>52</v>
       </c>
       <c r="M68" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
       <c r="B69" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C69" t="s">
         <v>60</v>
@@ -4576,80 +4588,80 @@
         <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F69" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G69" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H69" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I69" t="s">
         <v>27</v>
       </c>
       <c r="J69" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K69" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L69" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M69" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C70" t="s">
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E70" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F70" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K70" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L70" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M70" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
       <c r="B71" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C71" t="s">
         <v>1</v>
@@ -4661,36 +4673,36 @@
         <v>154</v>
       </c>
       <c r="F71" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H71" t="s">
         <v>68</v>
       </c>
       <c r="I71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J71" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L71" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M71" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
       <c r="B72" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C72" t="s">
         <v>60</v>
@@ -4702,92 +4714,92 @@
         <v>27</v>
       </c>
       <c r="F72" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G72" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H72" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J72" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K72" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L72" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M72" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
       <c r="B73" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C73" t="s">
         <v>43</v>
       </c>
       <c r="D73" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E73" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F73" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G73" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H73" t="s">
         <v>68</v>
       </c>
       <c r="I73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J73" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K73" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L73" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M73" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
       <c r="B74" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C74" t="s">
         <v>51</v>
       </c>
       <c r="D74" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E74" t="s">
         <v>32</v>
       </c>
       <c r="F74" t="s">
+        <v>334</v>
+      </c>
+      <c r="G74" t="s">
         <v>332</v>
-      </c>
-      <c r="G74" t="s">
-        <v>330</v>
       </c>
       <c r="H74" t="s">
         <v>154</v>
@@ -4796,24 +4808,24 @@
         <v>68</v>
       </c>
       <c r="J74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K74" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L74" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M74" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
       <c r="B75" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C75" t="s">
         <v>55</v>
@@ -4822,45 +4834,45 @@
         <v>89</v>
       </c>
       <c r="E75" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G75" t="s">
         <v>154</v>
       </c>
       <c r="H75" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J75" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K75" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L75" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M75" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
       <c r="B76" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C76" t="s">
         <v>60</v>
       </c>
       <c r="D76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E76" t="s">
         <v>142</v>
@@ -4869,19 +4881,19 @@
         <v>74</v>
       </c>
       <c r="G76" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I76" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J76" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K76" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L76" t="s">
         <v>106</v>
@@ -4890,39 +4902,39 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
       <c r="B77" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C77" t="s">
         <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E77" t="s">
         <v>153</v>
       </c>
       <c r="F77" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G77" t="s">
         <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I77" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J77" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K77" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L77" t="s">
         <v>48</v>
@@ -4931,258 +4943,258 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
       <c r="B78" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C78" t="s">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E78" t="s">
         <v>157</v>
       </c>
       <c r="F78" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G78" t="s">
         <v>119</v>
       </c>
       <c r="H78" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I78" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J78" t="s">
         <v>90</v>
       </c>
       <c r="K78" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L78" t="s">
         <v>111</v>
       </c>
       <c r="M78" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
       <c r="B79" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C79" t="s">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E79" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F79" t="s">
         <v>48</v>
       </c>
       <c r="G79" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H79" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I79" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K79" t="s">
         <v>148</v>
       </c>
       <c r="L79" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M79" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
       <c r="B80" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C80" t="s">
         <v>43</v>
       </c>
       <c r="D80" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E80" t="s">
         <v>48</v>
       </c>
       <c r="F80" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G80" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H80" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I80" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J80" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K80" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L80" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M80" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
       <c r="B81" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C81" t="s">
         <v>60</v>
       </c>
       <c r="D81" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E81" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F81" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G81" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H81" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I81" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J81" t="s">
         <v>30</v>
       </c>
       <c r="K81" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L81" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M81" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C82" t="s">
         <v>51</v>
       </c>
       <c r="D82" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E82" t="s">
         <v>157</v>
       </c>
       <c r="F82" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H82" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I82" t="s">
         <v>148</v>
       </c>
       <c r="J82" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K82" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L82" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M82" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
       <c r="B83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C83" t="s">
         <v>55</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E83" t="s">
         <v>157</v>
       </c>
       <c r="F83" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G83" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H83" t="s">
         <v>119</v>
       </c>
       <c r="I83" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J83" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K83" t="s">
         <v>148</v>
       </c>
       <c r="L83" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M83" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
       <c r="B84" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C84" t="s">
         <v>0</v>
@@ -5209,36 +5221,36 @@
         <v>125</v>
       </c>
       <c r="K84" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M84" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
       <c r="B85" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C85" t="s">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E85" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G85" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H85" t="s">
         <v>89</v>
@@ -5247,24 +5259,24 @@
         <v>32</v>
       </c>
       <c r="J85" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L85" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M85" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
       <c r="B86" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C86" t="s">
         <v>43</v>
@@ -5276,7 +5288,7 @@
         <v>130</v>
       </c>
       <c r="F86" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G86" t="s">
         <v>136</v>
@@ -5291,21 +5303,21 @@
         <v>125</v>
       </c>
       <c r="K86" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L86" t="s">
         <v>15</v>
       </c>
       <c r="M86" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
       <c r="B87" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C87" t="s">
         <v>51</v>
@@ -5314,10 +5326,10 @@
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F87" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G87" t="s">
         <v>76</v>
@@ -5326,77 +5338,77 @@
         <v>147</v>
       </c>
       <c r="I87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J87" t="s">
         <v>105</v>
       </c>
       <c r="K87" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L87" t="s">
         <v>54</v>
       </c>
       <c r="M87" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
       <c r="B88" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C88" t="s">
         <v>55</v>
       </c>
       <c r="D88" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F88" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G88" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H88" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I88" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J88" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K88" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L88" t="s">
         <v>54</v>
       </c>
       <c r="M88" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
       <c r="B89" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C89" t="s">
         <v>158</v>
       </c>
       <c r="D89" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
         <v>120</v>
@@ -5408,153 +5420,153 @@
         <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J89" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K89" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L89" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M89" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
       <c r="B90" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D90" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E90" t="s">
         <v>117</v>
       </c>
       <c r="F90" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G90" t="s">
         <v>89</v>
       </c>
       <c r="H90" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I90" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J90" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K90" t="s">
         <v>118</v>
       </c>
       <c r="L90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M90" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
       <c r="B91" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C91" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F91" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G91" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H91" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J91" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K91" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L91" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M91" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
       <c r="B92" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C92" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D92" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
         <v>117</v>
       </c>
       <c r="F92" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G92" t="s">
         <v>154</v>
       </c>
       <c r="H92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I92" t="s">
         <v>118</v>
       </c>
       <c r="J92" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K92" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L92" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M92" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
       <c r="B93" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C93" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D93" t="s">
         <v>152</v>
@@ -5566,95 +5578,95 @@
         <v>108</v>
       </c>
       <c r="G93" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H93" t="s">
         <v>118</v>
       </c>
       <c r="I93" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J93" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K93" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L93" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M93" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
       <c r="B94" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C94" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F94" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G94" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H94" t="s">
         <v>68</v>
       </c>
       <c r="I94" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J94" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K94" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L94" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M94" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
       <c r="B95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C95" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D95" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E95" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F95" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G95" t="s">
         <v>19</v>
       </c>
       <c r="H95" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I95" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J95" t="s">
         <v>136</v>
@@ -5666,71 +5678,71 @@
         <v>53</v>
       </c>
       <c r="M95" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
       <c r="B96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C96" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D96" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F96" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G96" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H96" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I96" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J96" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K96" t="s">
         <v>62</v>
       </c>
       <c r="L96" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M96" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
       <c r="B97" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D97" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E97" t="s">
         <v>117</v>
       </c>
       <c r="F97" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G97" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H97" t="s">
         <v>89</v>
@@ -5739,45 +5751,45 @@
         <v>154</v>
       </c>
       <c r="J97" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K97" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L97" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M97" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
       <c r="B98" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C98" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D98" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E98" t="s">
         <v>87</v>
       </c>
       <c r="F98" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G98" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H98" t="s">
         <v>120</v>
       </c>
       <c r="I98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J98" t="s">
         <v>15</v>
@@ -5786,30 +5798,30 @@
         <v>19</v>
       </c>
       <c r="L98" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M98" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
       <c r="B99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C99" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E99" t="s">
         <v>117</v>
       </c>
       <c r="F99" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G99" t="s">
         <v>154</v>
@@ -5818,71 +5830,71 @@
         <v>118</v>
       </c>
       <c r="I99" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J99" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L99" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M99" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
       <c r="B100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C100" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D100" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F100" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G100" t="s">
         <v>68</v>
       </c>
       <c r="H100" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I100" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J100" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K100" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L100" t="s">
         <v>26</v>
       </c>
       <c r="M100" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
       <c r="B101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C101" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -5897,83 +5909,83 @@
         <v>62</v>
       </c>
       <c r="H101" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I101" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J101" t="s">
         <v>136</v>
       </c>
       <c r="K101" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L101" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M101" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
       <c r="B102" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C102" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D102" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E102" t="s">
         <v>118</v>
       </c>
       <c r="F102" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G102" t="s">
         <v>117</v>
       </c>
       <c r="H102" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I102" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J102" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L102" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M102" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
       <c r="B103" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C103" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D103" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E103" t="s">
         <v>117</v>
       </c>
       <c r="F103" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G103" t="s">
         <v>118</v>
@@ -5982,30 +5994,30 @@
         <v>154</v>
       </c>
       <c r="I103" t="s">
+        <v>184</v>
+      </c>
+      <c r="J103" t="s">
+        <v>283</v>
+      </c>
+      <c r="K103" t="s">
+        <v>405</v>
+      </c>
+      <c r="L103" t="s">
+        <v>161</v>
+      </c>
+      <c r="M103" t="s">
         <v>183</v>
       </c>
-      <c r="J103" t="s">
-        <v>281</v>
-      </c>
-      <c r="K103" t="s">
-        <v>403</v>
-      </c>
-      <c r="L103" t="s">
-        <v>160</v>
-      </c>
-      <c r="M103" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
       <c r="B104" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C104" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D104" t="s">
         <v>130</v>
@@ -6014,10 +6026,10 @@
         <v>66</v>
       </c>
       <c r="F104" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G104" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H104" t="s">
         <v>136</v>
@@ -6029,21 +6041,21 @@
         <v>15</v>
       </c>
       <c r="K104" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L104" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M104" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
       <c r="B105" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C105" t="s">
         <v>60</v>
@@ -6052,66 +6064,66 @@
         <v>121</v>
       </c>
       <c r="E105" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F105" t="s">
         <v>64</v>
       </c>
       <c r="G105" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H105" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I105" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J105" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K105" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L105" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M105" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
       <c r="B106" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C106" t="s">
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E106" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F106" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G106" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H106" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I106" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J106" t="s">
         <v>111</v>
       </c>
       <c r="K106" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L106" t="s">
         <v>149</v>
@@ -6120,12 +6132,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
       <c r="B107" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C107" t="s">
         <v>1</v>
@@ -6134,54 +6146,54 @@
         <v>50</v>
       </c>
       <c r="E107" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F107" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G107" t="s">
         <v>93</v>
       </c>
       <c r="H107" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I107" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J107" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K107" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L107" t="s">
         <v>48</v>
       </c>
       <c r="M107" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
       <c r="B108" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C108" t="s">
         <v>51</v>
       </c>
       <c r="D108" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E108" t="s">
         <v>48</v>
       </c>
       <c r="F108" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G108" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H108" t="s">
         <v>93</v>
@@ -6190,80 +6202,80 @@
         <v>28</v>
       </c>
       <c r="J108" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K108" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L108" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M108" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
       <c r="B109" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C109" t="s">
         <v>55</v>
       </c>
       <c r="D109" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E109" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F109" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G109" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H109" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I109" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J109" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K109" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L109" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M109" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
       <c r="B110" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C110" t="s">
         <v>158</v>
       </c>
       <c r="D110" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E110" t="s">
         <v>106</v>
       </c>
       <c r="F110" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G110" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H110" t="s">
         <v>93</v>
@@ -6272,30 +6284,30 @@
         <v>148</v>
       </c>
       <c r="J110" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K110" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L110" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M110" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
       <c r="B111" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C111" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D111" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E111" t="s">
         <v>143</v>
@@ -6304,39 +6316,39 @@
         <v>106</v>
       </c>
       <c r="G111" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H111" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I111" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J111" t="s">
         <v>142</v>
       </c>
       <c r="K111" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L111" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M111" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
       <c r="B112" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C112" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D112" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E112" t="s">
         <v>143</v>
@@ -6345,33 +6357,33 @@
         <v>106</v>
       </c>
       <c r="G112" t="s">
+        <v>182</v>
+      </c>
+      <c r="H112" t="s">
+        <v>432</v>
+      </c>
+      <c r="I112" t="s">
+        <v>435</v>
+      </c>
+      <c r="J112" t="s">
+        <v>426</v>
+      </c>
+      <c r="K112" t="s">
+        <v>363</v>
+      </c>
+      <c r="L112" t="s">
+        <v>242</v>
+      </c>
+      <c r="M112" t="s">
         <v>181</v>
       </c>
-      <c r="H112" t="s">
-        <v>430</v>
-      </c>
-      <c r="I112" t="s">
-        <v>433</v>
-      </c>
-      <c r="J112" t="s">
-        <v>424</v>
-      </c>
-      <c r="K112" t="s">
-        <v>361</v>
-      </c>
-      <c r="L112" t="s">
-        <v>240</v>
-      </c>
-      <c r="M112" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
       <c r="B113" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C113" t="s">
         <v>60</v>
@@ -6386,42 +6398,42 @@
         <v>17</v>
       </c>
       <c r="G113" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H113" t="s">
-        <v>18</v>
+        <v>436</v>
       </c>
       <c r="I113" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J113" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K113" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L113" t="s">
         <v>114</v>
       </c>
       <c r="M113" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
       <c r="B114" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C114" t="s">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F114" t="s">
         <v>58</v>
@@ -6436,7 +6448,7 @@
         <v>79</v>
       </c>
       <c r="J114" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K114" t="s">
         <v>80</v>
@@ -6448,53 +6460,53 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
       <c r="B115" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C115" t="s">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E115" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F115" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G115" t="s">
         <v>29</v>
       </c>
       <c r="H115" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="I115" t="s">
         <v>75</v>
       </c>
       <c r="J115" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K115" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L115" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M115" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
       <c r="B116" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C116" t="s">
         <v>43</v>
@@ -6503,63 +6515,63 @@
         <v>26</v>
       </c>
       <c r="E116" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F116" t="s">
         <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="H116" t="s">
-        <v>171</v>
+        <v>447</v>
       </c>
       <c r="I116" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J116" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K116" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L116" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M116" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
       <c r="B117" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C117" t="s">
         <v>51</v>
       </c>
       <c r="D117" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E117" t="s">
-        <v>171</v>
+        <v>447</v>
       </c>
       <c r="F117" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G117" t="s">
         <v>75</v>
       </c>
       <c r="H117" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I117" t="s">
         <v>80</v>
       </c>
       <c r="J117" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K117" t="s">
         <v>27</v>
@@ -6571,45 +6583,45 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
       <c r="B118" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C118" t="s">
         <v>55</v>
       </c>
       <c r="D118" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E118" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F118" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G118" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H118" t="s">
         <v>145</v>
       </c>
       <c r="I118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J118" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K118" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L118" t="s">
         <v>103</v>
       </c>
       <c r="M118" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -518,7 +518,7 @@
     <t>Stage 6</t>
   </si>
   <si>
-    <t>T. H. Johannessen</t>
+    <t>Tobias Halland Johannessen</t>
   </si>
   <si>
     <t>David Gaudu</t>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -530,7 +530,7 @@
     <t>Stage 7</t>
   </si>
   <si>
-    <t>T. T. Teutenberg</t>
+    <t>Tim Torn Teutenberg</t>
   </si>
   <si>
     <t>Hugo Hofstetter</t>
@@ -596,7 +596,7 @@
     <t>Egan Bernal</t>
   </si>
   <si>
-    <t>Jefferson Cepeda</t>
+    <t>Jefferson Alveiro Cepeda</t>
   </si>
   <si>
     <t>Igor Arrieta</t>
@@ -674,7 +674,7 @@
     <t>Milan Fretin</t>
   </si>
   <si>
-    <t>S. Koller Løland</t>
+    <t>Sakarias Koller Løland</t>
   </si>
   <si>
     <t>Axel Zingle</t>
